--- a/input/汇总_预置资源.xlsx
+++ b/input/汇总_预置资源.xlsx
@@ -363,811 +363,778 @@
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2">
-        <v>997651001481</v>
+        <v>1007173688145</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26年AI归来考研英语一英二全套电子版资料PDF来啦！英一英二通用，大作文+小作文模板+历年主题词汇+答题卡全都有，备考冲刺必备！
-内容包括：2026考研英语作文模板PDF（英一英二通用）、大作文模板、小作文模板、历年主题词汇、答题卡等，数字资源，拍下自动发网盘链接，秒下不用等！
-需要具体资料内容可以私聊，欢迎咨询，喜欢直接拍，有问题随时问我～
-免责声明：资料只限学习用途，不得用于商业，标价为收集整理资料的辛苦费，虚拟商品售出不退不换，介意勿拍！
-学习资料定制，喜欢就拍，细节私聊！
-</t>
+          <t>78套2026马年工作计划总结PPT模板78套2026马年工作计划PPT模板 年会总结述职汇报开门红|||PPT素材
+[比心]内容包含
+[右]78套适配2026马年的工作计划PPT模板
+[右]马年主题元素：融入骏马、新年氛围等专属设计
+[右]全场景适配：工作计划/年终总结/述职汇报/年会等均可使用
+[右]一键编辑：文字、图片、图表均可修改，操作简单
+[比心]售后说明
+[比心]
+[1]. 电子资料通过网盘发送，秒拍秒发，24小时自动发货；
+[2]. 电子资料具有可复制性，一经售出不支持无理由退款，下单前先确认需求，避免不必要纠纷；
+[3]. 所分享资源均来源于互联网，版权归原作者所有，若存在侵权问题，麻烦联系我处理。#闲鱼还能卖这个？ #发布技能来赚钱</t>
         </is>
       </c>
       <c r="C2" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/2219202947442/O1CN01K9902U24qUd1Jl87q_!!4611686018427382130-0-xy_item.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/2219202947442/O1CN01K9902U24qUd1Jl87q_!!4611686018427382130-0-xy_item.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i2/2219202947442/O1CN01K9902U24qUd1Jl87q_!!4611686018427382130-0-xy_item.jpg_790x10000Q90.jpg_.webp</v>
-      </c>
-      <c r="D2" s="2"/>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/2218894703320/O1CN01TJcmFJ1aOc3FkOWzF_!!4611686018427386584-0-xy_item.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/2218894703320/O1CN01TJcmFJ1aOc3FkOWzF_!!4611686018427386584-0-xy_item.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i4/2218894703320/O1CN01TJcmFJ1aOc3FkOWzF_!!4611686018427386584-0-xy_item.jpg_790x10000Q90.jpg_.webp</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.22e26c82v4o1nV&amp;id=1007173688145&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.22e26c82v4o1nV&amp;id=1007173688145&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.22e26c82v4o1nV&amp;id=1007173688145&amp;categoryId=201454708</v>
+      </c>
     </row>
     <row r="3" ht="25.5" customHeight="1">
       <c r="A3">
-        <v>950132739399</v>
+        <v>948022201397</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>【BEC商务英语】2025最新整理版初级➕中级➕高级全部课程
-[号外][号外][号外][号外]
-35个学习文档资料
-真题+解析+音频+视频
-BEC高级、中级、初级课程
-高级、中级、初级全程通关
-格式：PDF、Word、MP3等
-适用对象：
-准备参加BEC考试的考生
-商务英语学习者
-希望提升商务英语水平的专业人士
-发货方式：百度网盘自动发货
-价格：标价即卖价，直接拍即可
-特点：
-最新整理：2025年最新整理版，确保内容的时效性和准确性。
-多种资源：包括讲义、笔记、真题、解析、音频等多种学习资源。
-[火][火][火]内容概述
-1. 35个学习文档资料：
-包括词汇表、语法讲解、写作模板、口语练习材料等。
-详细的备考指南和复习计划。
-[钉子][钉子][钉子]真题+解析+音频：
-近年的BEC考试真题及详细解析。
-配套的听力音频文件，方便进行听力训练。
-[钉子][钉子][钉子]
-4. 高级、中级、初级全程通关课。
-全面的备考指导和技巧分享。
-注意事项
-虚拟商品：由于是电子文件，具有可复制性，一经售出概不退换，请谨慎购买。
-安全提示：请从信誉良好的卖家处购买，并确保下载的文件来源可靠，以避免潜在的安全风险。
-链接失效：如果下载链接失效，可以联系卖家补发新的链接。
-[[号外][号外][号外]祝您学习顺利，取得优异成绩！火火火火火火666
-资料仅做分享，赚的是整理资料的辛苦费用</t>
+          <t>【秒发】领导超爱的高级感工作汇报PPT模版 逻辑图 数据图|||
+排版简洁干净，高端大气，打工人必备！
+九个模版九种配色 每套160页
+附赠：国外高端PPT模版（400p）、常用小图标、字体包
+由于电子教程的可复制性，发货后不得退款，敬请谅解！
+【免责声明】
+上架资源均由个人亲自整理 且标注免责声明以及对应图片 具体内容如下:
+1.所有文件均获取自网络公开渠道，仅供学习和交流使用，所有版权归版权人所有。
+2.如版权方认为侵犯了您的版权，请及时联系小店删除
+3.本店所有商品售价仅是对资源查找以及整理的加工费用，如喜欢作品，请支持正版哦~
+4.本店所有商品不涉及商用，仅是以众筹的于提供给想要学习的极少部分人用于学习。</t>
         </is>
       </c>
       <c r="C3" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/1732655361/O1CN01unLIqv1pTOPuiW3ep_!!4611686018427386113-0-xy_item.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/1732655361/O1CN01unLIqv1pTOPuiW3ep_!!4611686018427386113-0-xy_item.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/1732655361/O1CN01unLIqv1pTOPuiW3ep_!!4611686018427386113-0-xy_item.jpg_790x10000Q90.jpg_.webp</v>
-      </c>
-      <c r="D3" s="2"/>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN01d3mCf01IFlGr7C5OY_!!4611686018427383856-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN01d3mCf01IFlGr7C5OY_!!4611686018427383856-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i2/O1CN01d3mCf01IFlGr7C5OY_!!4611686018427383856-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.17.22e26c82jlohwD&amp;id=948022201397&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.17.22e26c82jlohwD&amp;id=948022201397&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.17.22e26c82jlohwD&amp;id=948022201397&amp;categoryId=201454708</v>
+      </c>
     </row>
     <row r="4" ht="25.5" customHeight="1">
       <c r="A4">
-        <v>799657546298</v>
+        <v>1007252038443</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025年高考一二轮总复习资料电子版高三英语文数学物理化学模拟真题PPT讲义历史生物地理政/治
-包括新高考23+24+2025全套总复习资料。
-2025年一二轮九科已更新到蕞新内容，后续持续更新，免费更新2026版新资料。
-送老高考23-24一轮+二轮+专项复习
-送模拟试卷
-内容有：PPT课件、讲义、习题、知识梳理、难点突破、真题汇编与模拟题等
-直接拍，无需等待，佰度䋞盘24h-自动秒发货。
-收货自动送：2025某pin牌教辅，榀牌知识点、知识手册、高考前蕞后一课等
+          <t>1200页数据分析ppt模板工作汇报ppt述职报告ppt高级感ppt模板
+素材包含工作报告21套，数据分析ppt不重复共1200页；
+适用范围：日常报告，市场调研，数据分析，工作总结，工作汇报，述职报告等各种场景；
+黄金曲线模型，SWOT模型，鱼骨图等可视化逻辑图表；
+一份好的ppt可以助力您的事业，节省您的时间；
+可编辑可修改，使用方便；
+——————★24小时自动发货★——————
+精心挑选ppt高端模板，简洁、高效、直观；
+✨每套模板都是我精心挑选的；
+✨每款精品质量高，助力您更加顺利～
+✨小说明：网页端、手机端可能存在兼容问题，如碰到PPT显示异常，请下载后使用电脑端office和wps打开～
+✨所有文件均获取自网络公开渠道，仅供学习和交流使用，如有侵权请及时联系小店删除。
 </t>
         </is>
       </c>
       <c r="C4" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i1/O1CN01GoRlal1zbJMvhYkYa_!!4611686018427384060-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i1/O1CN01GoRlal1zbJMvhYkYa_!!4611686018427384060-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i1/O1CN01GoRlal1zbJMvhYkYa_!!4611686018427384060-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
-      </c>
-      <c r="D4" s="2"/>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i1/O1CN01OPu8Ij1Tsej4lOraJ_!!4611686018427386534-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i1/O1CN01OPu8Ij1Tsej4lOraJ_!!4611686018427386534-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i1/O1CN01OPu8Ij1Tsej4lOraJ_!!4611686018427386534-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.13.22e26c82jlohwD&amp;id=1007252038443&amp;categoryId=201453706", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.13.22e26c82jlohwD&amp;id=1007252038443&amp;categoryId=201453706")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.13.22e26c82jlohwD&amp;id=1007252038443&amp;categoryId=201453706</v>
+      </c>
     </row>
     <row r="5" ht="25.5" customHeight="1">
       <c r="A5">
-        <v>959038414781</v>
+        <v>1013420928028</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>【0.1 自动秒发】黄夫人物理高一高二 高三同步课视频 包含500多个视频，一轮复习讲义网义，高一高二高三讲义等
-黄夫人全集包含
-1.高一高二高三同步课视频
-2.高三电子版讲义，专题讲解
-3.选修合集，黄夫人高一高二高三讲义
-4.高三一轮复习
-5.必修1-4（文案图片均来自真实资料）
-拍下后百度网盘24小时自动发货，仅收取整理费用，如有侵权联系删除
+          <t>【双盘秒发】期末表彰大会PPT模板可编辑小学初中通用含班主任致辞颁奖典礼寒假安全提示
+期末表彰大会PPT模板来啦！适用于小学、初中、高中各年级，内容完整，氛围感十足。模板已设计好，可直接使用，轻松替换文字和图片，省时省力。
+班主任致辞页面
+颁奖典礼环节
+寒假安全提示
+假期安排建议
+总结与展望模块
+模板风格简洁大气，贴合校园主题，帮你高效组织期末表彰活动，传递鼓励与关怀。
+【适用场景】
+班级期末总结
+学校表彰大会
+年级集体会议
+线上表彰活动
+2025年辛勤耕耘，2026年继续努力！用一份用心制作的PPT，为学期画上圆满句号。
+注：本商品为电子版PPT模板，购买后发送网盘链接，请及时下载。
+免责声明：版权归属原作者。如认为侵犯版权，请及时通知小店删除。支持正版，敬请前往官方购买。
 </t>
         </is>
       </c>
       <c r="C5" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i1/O1CN01FpvIab26jjzdIFUfX_!!4611686018427387058-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i1/O1CN01FpvIab26jjzdIFUfX_!!4611686018427387058-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i1/O1CN01FpvIab26jjzdIFUfX_!!4611686018427387058-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
-      </c>
-      <c r="D5" s="2"/>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/2221187899404/O1CN01GeWI572JL5ih8UiOo_!!4611686018427379724-53-xy_item.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/2221187899404/O1CN01GeWI572JL5ih8UiOo_!!4611686018427379724-53-xy_item.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i2/2221187899404/O1CN01GeWI572JL5ih8UiOo_!!4611686018427379724-53-xy_item.heic_790x10000Q90.jpg_.webp</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.21.22e26c82v4o1nV&amp;id=1013420928028&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.21.22e26c82v4o1nV&amp;id=1013420928028&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.21.22e26c82v4o1nV&amp;id=1013420928028&amp;categoryId=201454708</v>
+      </c>
     </row>
     <row r="6" ht="25.5" customHeight="1">
       <c r="A6">
-        <v>790614146039</v>
+        <v>914239405011</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>《C语言》 重点 考点 题库 资料合集 全部发！就是标价！
-期末复习资料 抱佛脚必备
-【直接拍下发全部，网盘发货】
-内容包括
-①C语言常考知识点大总结[14页】
-②C语言程序设计知识点总结【11页】
-③C语言课件（精华版）【629张】
-④C语言学习笔记[110页】
-⑤C语言知识点总结【14页】
-⑥题库1-C语言分章习题库附答案【90页】
-⑦题库2-C语言分章习题集附答案【50页】
-⑧题库3-c语言10套卷含答案【32页】
-⑨题库4-C语言程序改错题库【80页】
-10-题库5-大学C语言期末试题与答案【55页】
-11-题库6-C语言程序填空题库【28页】
-12-题库7-C语言程序设计模拟试题及答案【6页】
-13-题库8-C语言程序模拟试题【8页】
-14-题库9-c语言经典程序题目【12页】
-15-题库10-C语言复习题库【18页】
---
-适用于考研初试学习，考研复试面试，保研面笔试、夏令营面试、九推复试面试、自考、期末考试等情况，也避免出现老师进行专业问答时你不懂你尴尬，他尴尬，最后导致结果尴尬的局面
-Tag：考研专业课资料&amp;保研资料&amp;自考资料&amp;期末复习资料
-马上涨价，想要赶紧！（标价就是实价，直接拍）
+          <t>结构化PPT模板：述职汇报PPT、工作汇报、实习汇报、论文答辩、财务分析、市场调研，模板内容可编辑
+适用范围：日常报告，市场调研，数据分析，工作总结，工作汇报，品牌效应……等各种场景
+黄金曲线模型，SWOT模型，冰山模型，鱼骨图……应有尽有
+300页高级逻辑数据PPT（赠500页汇报PPT）｜6种配色替换｜工作汇报、数据复盘、年中总结、个人介绍均适用｜可编辑数据｜打包价出！
+天蝎PPT，柠檬PPT，青云PPT，唐峰素材，荔枝PPT，物语PPT，小李在做PPT，物语PPT，狗哥在做PPT，芝士PPT 全都有
+精美数据图
+精美逻辑图
+工作汇报
+可视化图表（可编辑）持续更新ing
+拍后赠送图标素材、工作汇报图标库、字体包
+原价拍下只发一个博主随时可拍，发送百度网盘链接，发后不退！建议看清楚再下单。
 </t>
         </is>
       </c>
       <c r="C6" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i3/O1CN01vLz6cV2JnU9eV6oKs_!!0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i3/O1CN01vLz6cV2JnU9eV6oKs_!!0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i3/O1CN01vLz6cV2JnU9eV6oKs_!!0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
-      </c>
-      <c r="D6" s="2"/>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN01OzZTsM1SnKR67WAbL_!!4611686018427381555-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN01OzZTsM1SnKR67WAbL_!!4611686018427381555-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i2/O1CN01OzZTsM1SnKR67WAbL_!!4611686018427381555-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.24.22e26c82v4o1nV&amp;id=914239405011&amp;categoryId=201453706", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.24.22e26c82v4o1nV&amp;id=914239405011&amp;categoryId=201453706")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.24.22e26c82v4o1nV&amp;id=914239405011&amp;categoryId=201453706</v>
+      </c>
     </row>
     <row r="7" ht="25.5" customHeight="1">
       <c r="A7">
-        <v>942018152068</v>
+        <v>1015152429455</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>人教版1-6年级小学数学知识点考点归纳汇总（彩色版共92页）非实物
-1. 完整的 1-6 年级数学上册+下册知识点。
-2. 彩色高清手写字体，分单元呈现清晰。
-3. 知识点、复习要点清晰可见超详细。
-一年级上下册共9页
-二年级上下册共10页
-三年级上下册共15页
-四年级上下册共16页
-五年级上下册共19页
-六年级上下册共23页
-额外赠送1-6年级复习提纲、易错清单、预习要点等，赠送的东西太多，物超所值。
-[1]标价全套价格，拍下自动发货
-[2电孑资料，无实物，【度盘+夸盘】自动发送
-[3]电孑文档的可复制性，一经拍下概不退换</t>
+          <t>【马年企业年会PPT模板】红色大气风格，适合公司年会、员工表彰、颁奖典礼、团队荣誉展示等场合～
+内容超全，包含数说辉煌、荣誉共襄、艺展芳华、乐启新章等模块，页数多，直接套用，省时省力！
+高清PPT格式，支持编辑，图片文字都能改，内容可添加，适合企业、学校、个人年会用。
+拍下秒发百度网盘链接，虚拟商品不退不换，有问题随时私聊，喜欢直接拍！
+</t>
         </is>
       </c>
       <c r="C7" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01m22qEs1lijAkrIAnt_!!4611686018427384645-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01m22qEs1lijAkrIAnt_!!4611686018427384645-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/O1CN01m22qEs1lijAkrIAnt_!!4611686018427384645-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
-      </c>
-      <c r="D7" s="2"/>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/2215524546353/O1CN01TrMYWz1wnjKBlRUrN_!!4611686018427385649-0-xy_item.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/2215524546353/O1CN01TrMYWz1wnjKBlRUrN_!!4611686018427385649-0-xy_item.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i2/2215524546353/O1CN01TrMYWz1wnjKBlRUrN_!!4611686018427385649-0-xy_item.jpg_790x10000Q90.jpg_.webp</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.19.22e26c82v4o1nV&amp;id=1015152429455&amp;categoryId=201453706", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.19.22e26c82v4o1nV&amp;id=1015152429455&amp;categoryId=201453706")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.19.22e26c82v4o1nV&amp;id=1015152429455&amp;categoryId=201453706</v>
+      </c>
     </row>
     <row r="8" ht="25.5" customHeight="1">
       <c r="A8">
-        <v>948726934630</v>
+        <v>1005329106185</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025新版七年级上册语文人教版复习预习全套资料
-还在为孩子七年级上册语文的复习和预习发愁吗？看这里，全套资料来袭，让孩子学习无忧！
-总共473个文件 ，内容超全，几乎都是按照课文或者单元编写。预习资料帮孩子在开学前抢占先机，早背晚默资料助力基础知识的积累，知识点梳理类、重点归纳资料让孩子对知识掌握更透彻。古诗文文言文专题、名著专题，让孩子深入理解经典。期中期末复习专题帮孩子在考试前高效冲刺，作文提分指导和阅读答题技巧更是提升语文综合素养的关键。
-内容太多，无法一一展示，要是有需要可以私信我预览文件！
-下面给大家罗列一下顶层文件夹的名字，让大家更直观了解资料内容：
-- 七上语文必背内容汇总 - 2025
-- 七上语文基础字词句成语
-- 七上语文每课一练 - 2025
-- 七上语文一课一附 - 2025
-- 七上语文早背晚默写 - 2025
-- 七上语文重点知识归纳总结 - 2025
-- 七上语文单元知识清单 - 2025
-- 七上语文单元检测卷 - 2025
-- 七上语文古诗文 + 文言文训练 - 2025
-- 七上语文必读名著《朝花夕拾》+《西游记》-2025
-- 七上语文月考测试卷 - 2025
-- 七上语文期中复习专题
-- 七上语文期末复习专题
-- 七上语文单元主题阅读 + 理解技巧 - 2025
-- 七上语文作文提分指导 - 2025
-拍下后，百度网盘链接发送，自动发货，标价就是卖价，需要直接拍！让孩子快人一步，轻松学好七年级上册语文！
-</t>
+          <t>2026马年年会活动邀请函长图年终总结答谢会海报模板PSD设计素材
+——★12小时自动秒发网盘 ★——
+——★12小时自动秒发网盘 ★——
+——★12小时自动秒发网盘 ★——
+秒拍秒发，拍下即发全部素材！各类所需素材一站式配齐，若不满意可直接退款～
+若未及时回复，可先下单查看内容，无需或不满意直接申请退款即可，上线后会第一时间处理，放心购买！
+预览图与源文件一一对应，仅售模板本身，无任何隐藏费用；使用过程中遇问题可随时咨询，如果不会使用可以咨询解决～
+每套模板均经过精心筛选，品质优质，适配学习展示、工作汇报、教学课件、商务提案等多场景，覆盖大学生、上班族、教师等不同人群，按风格单独归类并标注文档编号，查找更便捷～</t>
         </is>
       </c>
       <c r="C8" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01IAjcpA1U0RPdTUXmq_!!4611686018427386903-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01IAjcpA1U0RPdTUXmq_!!4611686018427386903-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/O1CN01IAjcpA1U0RPdTUXmq_!!4611686018427386903-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01NvWvM81IFlJUuRqRF_!!4611686018427383856-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01NvWvM81IFlJUuRqRF_!!4611686018427383856-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i4/O1CN01NvWvM81IFlJUuRqRF_!!4611686018427383856-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D8" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.5.1b377e61Ma7Ms3&amp;id=948726934630&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.5.1b377e61Ma7Ms3&amp;id=948726934630&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.5.1b377e61Ma7Ms3&amp;id=948726934630&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.22e26c82jlohwD&amp;id=1005329106185&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.22e26c82jlohwD&amp;id=1005329106185&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.22e26c82jlohwD&amp;id=1005329106185&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="9" ht="25.5" customHeight="1">
       <c r="A9">
-        <v>977151259449</v>
+        <v>879493972051</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>新人教a版高中数学选修必修课件教案，包含必修一二三和选修一二三全套电子版资料。
-专业整理：特聘100名一线特级教师参与整理编撰，更懂课堂！
-内容保障：优质PPT课件，精品教案，学习资料，紧跟教学前沿
-符合课改：符合新课改，教学设计规范标准，轻松应对检查！
-不论是老师备课，还是学生自学亦或是家长辅导，这份资料都是不二之选！
-注意事项：
-①电子资料，百度网盘发货
-②虚拟资料非实物，一经售出不退不换
-③支持百度网盘在线播放
-④标价仅为整理资料的辛苦费
-温馨提示：
-本店资料来源于网络公开渠道，仅供学习交流使用。资料不用于商业用途，仅作学习参考。如涉及侵权，请及时联系删除。
-喜欢的朋友可以直接下单哦～
+          <t>【自动发货】120套个人作品集ppt模板高级感作品集ppt
+适用于作品汇报、方案汇报ppt模板；
+艺术、创意、设计行业作品集；
+一份好的ppt可以助力您的事业，节省您的时间；
+每一款都设计精美，可编辑可修改，使用方便；
+———---★ 24小时自动发货 ★---———
+精心挑选ppt高端模板，简洁、高效、直观；
+✨每套模板都是我精心挑选的；
+✨每款精品质量高，助力您更加顺利～
+✨每一款都有预览图；
+虚拟物品售出不退不换噢！
+感兴趣的话快点击“我想要”来私聊吧！
 </t>
         </is>
       </c>
       <c r="C9" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i1/O1CN01eOIf1s2EIjZp6SeEI_!!4611686018427385506-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i1/O1CN01eOIf1s2EIjZp6SeEI_!!4611686018427385506-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i1/O1CN01eOIf1s2EIjZp6SeEI_!!4611686018427385506-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN0166n2vp1Tseddj6ATL_!!4611686018427386534-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN0166n2vp1Tseddj6ATL_!!4611686018427386534-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i4/O1CN0166n2vp1Tseddj6ATL_!!4611686018427386534-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D9" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.26.1b377e61Ma7Ms3&amp;id=977151259449&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.26.1b377e61Ma7Ms3&amp;id=977151259449&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.26.1b377e61Ma7Ms3&amp;id=977151259449&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.2.22e26c82v4o1nV&amp;id=879493972051&amp;categoryId=201453706", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.2.22e26c82v4o1nV&amp;id=879493972051&amp;categoryId=201453706")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.2.22e26c82v4o1nV&amp;id=879493972051&amp;categoryId=201453706</v>
       </c>
     </row>
     <row r="10" ht="25.5" customHeight="1">
       <c r="A10">
-        <v>993356819001</v>
+        <v>877213055621</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>【自动发货】2025新中特PDF及课后答案复习资料
-新时代中国特色社会主义理论与实践2024＋2021完整电子版复习资料PDF
-主要适用于研究生研一期末政治考试而定制。也适用于本科生，博士生，或者跟这个课程相关的人员。
-本人所用一手资料，资料更多。其他店铺盗取我的资料进行二次加工售卖的，资料内部含有他们自己店铺名称的广告图片或者链接，请大家注意甄别。
-资料更加完整，资料更多，基本涵盖了研究生政治考试所有的新中特复习资料。
-[1]所发文件包含2024和2021新中特复习资料考试总结整理知识点。其中，新中特重点资料文件夹共有5个文件，包含学校老师公布重点的pdf文件。
-[2]另外包括教材课后习题答案，二十大pdf，思考题答案，整理的考试重难点资料，开卷考试资料，某些大牛整理的资料
-[3]包含且不止如下资料
-1. 2024新中特单选题题库＋答案
-2. 2024新中特多选题题库＋答案
-3. 2024新中特课后习题及答案
-4. 2024新中特考试重难点
-5. 2024新中特考试论述题
-6. 2024新中特复习提纲
-7. 2024新中特电子书PDF
-8. 2024新中特复习重点笔记、复习要点、思考题等（补充资料）
-9. 附2021版新中特课件＋电子书＋课后思考题及答案
-10. 下面这两个都有哦
-新时代中国特色社会主义理论与实践PDF
-a.2021版新中特PDF+课后思考题重点及答案
-b.2024版新中特PDF+课后思考题重点及答案
-等等
-需要直接拍下秒发货，发百度网盘和夸克网盘链接，付款后7*24小时自动发送链接，无需等待。</t>
+          <t>7 色 560 页！数据分析可视化PPT模板，年终述职必备！
+主页置顶商品全店会员6.6，包含全店所有素材和以后更新的素材
+格式：PPT，可编辑，一键换色超便捷！
+丰富配色：精心调配7种时尚配色，深蓝、浅蓝、浅绿、橙蓝、红蓝、黑红、蓝橙灰，每种配色80页，共560页海量内容，满足多样审美。
+应用广泛：适用于日常报告、市场调研、数据分析、工作总结、工作汇报等各类场景，轻松应对职场各种展示需求。
+极速发货：全店24小时自动发货，拍下即发，百度网盘瞬间送达，无需漫长等待。
+#学习提升 #PPT模板 #数据分析 #年终述职
+</t>
         </is>
       </c>
       <c r="C10" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/3408357231/O1CN01U9A4VL23Hr3Y0jyK0_!!4611686018427381615-0-xy_item.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/3408357231/O1CN01U9A4VL23Hr3Y0jyK0_!!4611686018427381615-0-xy_item.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/3408357231/O1CN01U9A4VL23Hr3Y0jyK0_!!4611686018427381615-0-xy_item.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN018X8aPx1RRyKcFtJPb_!!4611686018427380973-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN018X8aPx1RRyKcFtJPb_!!4611686018427380973-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i2/O1CN018X8aPx1RRyKcFtJPb_!!4611686018427380973-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D10" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.10.1b377e61Ma7Ms3&amp;id=993356819001&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.10.1b377e61Ma7Ms3&amp;id=993356819001&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.10.1b377e61Ma7Ms3&amp;id=993356819001&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.4.22e26c82v4o1nV&amp;id=877213055621&amp;categoryId=201453706", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.4.22e26c82v4o1nV&amp;id=877213055621&amp;categoryId=201453706")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.4.22e26c82v4o1nV&amp;id=877213055621&amp;categoryId=201453706</v>
       </c>
     </row>
     <row r="11" ht="25.5" customHeight="1">
       <c r="A11">
-        <v>937046458029</v>
+        <v>1003949358886</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>【自动发货】毛概2025版 期末题库 最新版 24h秒发
-是大学老师给的
-有选择题、大题，简答题，有课后习题答案和复习笔记
-全部八章内容</t>
+          <t>【自动发货】2026马年年会元旦晚会互动小游戏ppt模板幼儿园小学新年晚会班会ppt模版
+2026马年年会小游戏PPT模板合集108款金马贺岁主题，适合企业年会、元旦晚会、幼儿园小学新年晚会等，互动性强，动画效果，现场气氛拉满！PPT成品直接用，规则和素材齐全，轻松搞定活动策划电子资料，拍下自动发，不用问在不在，直接下单即可，已开通自动发货
+25小时在线，拍下自动发货
+#年会礼品 #教学演示 #学习资料教材
+</t>
         </is>
       </c>
       <c r="C11" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01MPDI8822gkvuH9DtD_!!4611686018427385278-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01MPDI8822gkvuH9DtD_!!4611686018427385278-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/O1CN01MPDI8822gkvuH9DtD_!!4611686018427385278-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/2205299011153/O1CN013oSQQh1KO7mB9LnH4_!!4611686018427383377-53-xy_item.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/2205299011153/O1CN013oSQQh1KO7mB9LnH4_!!4611686018427383377-53-xy_item.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i2/2205299011153/O1CN013oSQQh1KO7mB9LnH4_!!4611686018427383377-53-xy_item.heic_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D11" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.29.1b377e61Ma7Ms3&amp;id=937046458029&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.29.1b377e61Ma7Ms3&amp;id=937046458029&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.29.1b377e61Ma7Ms3&amp;id=937046458029&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.22e26c82v4o1nV&amp;id=1003949358886&amp;categoryId=201453706", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.22e26c82v4o1nV&amp;id=1003949358886&amp;categoryId=201453706")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.22e26c82v4o1nV&amp;id=1003949358886&amp;categoryId=201453706</v>
       </c>
     </row>
     <row r="12" ht="25.5" customHeight="1">
       <c r="A12">
-        <v>903850991084</v>
+        <v>1001056572221</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>【电网资料】打包出【财会类】国家电网考试电子版资料。
-国网财会类专业包含财务管理、会计类、税务类、审计类、财务类等，具体专业见图。
-【更新】刚更新了25届题库、讲义和模拟卷！
-[1]含泪吐血整理，有多家机构，【独家】筛选并分类【最新】【核心】资料，即拿即用，节省复习时间。
-[2]网课视频、讲义、题库、真题模拟题和笔记，按需复习。更新25届大纲和解析版的企业文化（快速记忆方法），时政已更新到25年1月，含押题题库和重点题库。
-[3]拍前必看：图里的资料都有，需要就拍。
+          <t>蓝色高级PPT模板年终汇报总结述职报告工作汇报甘特图项目计划书
+——★12小时自动秒发网盘 ★——
+——★12小时自动秒发网盘 ★——
+——★12小时自动秒发网盘 ★——
+秒拍秒发，拍下即发全部素材！各类所需素材一站式配齐，若不满意可直接退款～
+若未及时回复，可先下单查看内容，无需或不满意直接申请退款即可，上线后会第一时间处理，放心购买！
+预览图与源文件一一对应，仅售模板本身，无任何隐藏费用；使用过程中遇问题可随时咨询，如果不会使用可以咨询解决～
+每套模板均经过精心筛选，品质优质，适配学习展示、工作汇报、教学课件、商务提案等多场景，覆盖大学生、上班族、教师等不同人群，按风格单独归类并标注文档编号，查找更便捷～
 </t>
         </is>
       </c>
       <c r="C12" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i1/O1CN01C9pSWT1Kgtx4TD0wi_!!4611686018427380330-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i1/O1CN01C9pSWT1Kgtx4TD0wi_!!4611686018427380330-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i1/O1CN01C9pSWT1Kgtx4TD0wi_!!4611686018427380330-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i3/O1CN01suWb7l1IFlJHOz7yn_!!4611686018427383856-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i3/O1CN01suWb7l1IFlJHOz7yn_!!4611686018427383856-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i3/O1CN01suWb7l1IFlJHOz7yn_!!4611686018427383856-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D12" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.5.1b377e61Ma7Ms3&amp;id=903850991084&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.5.1b377e61Ma7Ms3&amp;id=903850991084&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.5.1b377e61Ma7Ms3&amp;id=903850991084&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.17.22e26c82v4o1nV&amp;id=1001056572221&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.17.22e26c82v4o1nV&amp;id=1001056572221&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.17.22e26c82v4o1nV&amp;id=1001056572221&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="13" ht="25.5" customHeight="1">
       <c r="A13">
-        <v>939071072800</v>
+        <v>1018149740987</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>【非常全面】自考15040《新思想概论》
-资料很全含2504精讲视频、2504串讲、历年真题（更新到最新）、讲义、复习资料！
-发货：拍下速发度盘。
-退换：电子版资料，一经售出，不退不换，敬请谅解！
-赠送：复习资料
-拍下默认自动发本科目全部资料
-全部为高清版，可网盘在线观看！
-格式排版清晰，可直接打印！
-有遗漏或者链接失效请私信我，看到后立即解决！！！
-祝所有考生顺利通关，拿本科证！
+          <t>挑战杯小挑省国奖获奖作品创赛PPT模板大学生创业计划竞赛计划书
+——★24小时自动秒发百度网盘 ★——
+——★24小时自动秒发百度网盘 ★——
+——★24小时自动秒发百度网盘 ★——
+✨大赛资料包-2026年更新 挑战杯小挑
+✨40套省国奖-获奖案例[最新24年)
+✨6000份商业计划案例-word和PPT
+✨399套创赛类通用高端PPT模板
+✨精选26套完整案例配套Word+PPT
+评价有礼店铺内任选一个宝贝！！！
+任何不满意可直接退款！！！
+预览图对应相应源文件名字！！！！！
+没有任何额外费用，如果不会使用可以咨询解决！！！！
 </t>
         </is>
       </c>
       <c r="C13" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i3/O1CN01qe8hFN29PXLyXHCQD_!!4611686018427385676-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i3/O1CN01qe8hFN29PXLyXHCQD_!!4611686018427385676-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i3/O1CN01qe8hFN29PXLyXHCQD_!!4611686018427385676-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01PImTSA1dZ5yGGT51L_!!4611686018427387605-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01PImTSA1dZ5yGGT51L_!!4611686018427387605-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i4/O1CN01PImTSA1dZ5yGGT51L_!!4611686018427387605-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D13" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.28.1b377e61Ma7Ms3&amp;id=939071072800&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.28.1b377e61Ma7Ms3&amp;id=939071072800&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.28.1b377e61Ma7Ms3&amp;id=939071072800&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.22e26c82v4o1nV&amp;id=1018149740987&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.22e26c82v4o1nV&amp;id=1018149740987&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.22e26c82v4o1nV&amp;id=1018149740987&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="14" ht="25.5" customHeight="1">
       <c r="A14">
-        <v>946001438110</v>
+        <v>991471168227</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25新版《一本小学知识大盘点》电子PDF语文数学英语基本知识点复习一二三四五六年级全国通用
-小学1-6年级知识点全面盘点梳理。适合预习、复习使用，实用性强，性价比高。不分年级、版本，全国通用！
-高清pdf扫描版本，可自行打印！
-扫马看视频讲解，听音频
-2025最新版，不分版本，全国通用
-包含：（3科打包1元）
-语文：小学知识大盘点＋高频必刷题
-数学：小学知识大盘点＋思维导图
-英语：小学知识大盘点＋高频必刷题
-[绿圆]请看清说明，标价可以直接拍！
-[红圆]发百du网盘，链接永久有效，可随时查看转存下载！
-[蓝圆]pdf扫描版，非纸质，自行打印！
-免责申明:本店所有资料版权归原作者和出版社所有，标价仅为自己收集整理的辛苦费，不代表原实物价格。如有侵权，立删。
-</t>
+          <t>500页创意图文PPT模板，一键换图超实用！适合工作汇报、项目报告、策划方案等场景。包含多图排版、截图展示、人物介绍等多种模板，100%可编辑，用更少时间做出更高级的图文页面。标价就是卖价，24小时自动发货，网盘链接永久有效。
+[钉子][红圆][红圆][红圆][红圆][红圆][红圆][cool]网盘发货
+免责声明:
+[1].本店均通过网络等渠道合法获得，仅作为阅读交流使用，无任何商业目的。
+[2].本店商品价格是网盘储存费用和人工整理资料费用，并非资料本身价格。
+[3].本店为广大朋友提供音频视频资料学习，特此声明，版权归原作者所有，如有侵权请联系客服删除，谢谢!</t>
         </is>
       </c>
       <c r="C14" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN01sEDqHb2EK6kMmoWi4_!!4611686018427380485-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN01sEDqHb2EK6kMmoWi4_!!4611686018427380485-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i2/O1CN01sEDqHb2EK6kMmoWi4_!!4611686018427380485-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i1/O1CN01YP4zKm1vRSQfpAWCy_!!4611686018427386441-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i1/O1CN01YP4zKm1vRSQfpAWCy_!!4611686018427386441-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i1/O1CN01YP4zKm1vRSQfpAWCy_!!4611686018427386441-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D14" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.8.1b377e61Ma7Ms3&amp;id=946001438110&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.8.1b377e61Ma7Ms3&amp;id=946001438110&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.8.1b377e61Ma7Ms3&amp;id=946001438110&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.26.22e26c82v4o1nV&amp;id=991471168227&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.26.22e26c82v4o1nV&amp;id=991471168227&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.26.22e26c82v4o1nV&amp;id=991471168227&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="15" ht="25.5" customHeight="1">
       <c r="A15">
-        <v>857227411020</v>
+        <v>1001936052648</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>【秒发】2026年初级护师历年考试真题库答案解析彩色考点笔记难点资料汇总电子版pdf可下载可打印
-直接拍就行，秒发货，描述的都包含，bai度网盘发
-备考【26年初级护师】的姐妹们可以复习了。
-真题年份：2010-2025年都包含
-（题目与答案分开）
-2025年真题已更新，认准小雅资料，只有我这更新了，答案和题目也都是分开版，方便下载打印做题
-资料包含：
-1.真题【2010-2025年】+答案解析
-2.彩色考点笔记
-3.口诀速记
-4.计算公式
-5.模拟文档题
-6.送高频考题
-具体资料可以看下面图片上的文件夹，描述的都有，全部都发
-直接拍就行，秒发，整理不易，发出不退换，希望理解，记得给个好平哦
-</t>
+          <t>399套竞赛PPT国赛模板互联网+大学生创新创|||业大赛||| 挑战杯创赛等各类比赛各色系PPT案例PPT高端模板国金水平可以直接拍
+各种各样的高级精美模板都有需要的私信发模板图给你看，一共399套PPT全部带走，都是可编辑的源文件，主图个别不可编辑款已删除，每份都是超值的。
+【赠送】[1]500+套互联网＋，大创，挑战杯，往届获奖作品等资料参考，部分附带演示视频，
+【赠送】[2]大学生创新创业计划书word成品互联网+大赛ppt模板商业策划书撰写
+【赠送】[3]100个专业大学生职业生涯规划书Word范文赠送PPT
+拍下后网盘给您发货。标价就是卖价，不为赚米，交个朋友，24小时发货,标价就是卖价
+各类电子课程,资源。资源整理不易，收取的费用只是整理费用，版权归原作者所有，侵权联系删除。#学习资料教材</t>
         </is>
       </c>
       <c r="C15" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN01Czbgnb1RcxutKvZjZ_!!4611686018427380133-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN01Czbgnb1RcxutKvZjZ_!!4611686018427380133-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i2/O1CN01Czbgnb1RcxutKvZjZ_!!4611686018427380133-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01JbmD3x1IFlJJ4FH59_!!4611686018427383856-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01JbmD3x1IFlJJ4FH59_!!4611686018427383856-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i4/O1CN01JbmD3x1IFlJJ4FH59_!!4611686018427383856-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D15" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.27.1b377e61Ma7Ms3&amp;id=857227411020&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.27.1b377e61Ma7Ms3&amp;id=857227411020&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.27.1b377e61Ma7Ms3&amp;id=857227411020&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.25.22e26c82v4o1nV&amp;id=1001936052648&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.25.22e26c82v4o1nV&amp;id=1001936052648&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.25.22e26c82v4o1nV&amp;id=1001936052648&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="16" ht="25.5" customHeight="1">
       <c r="A16">
-        <v>975519024031</v>
+        <v>991558660076</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>最新版思想课期末冲刺包！复习笔记 考试题库 习题答案 知识点总结 大一到大三全覆盖
-标价直接拍
-考研政治笔试/考研马理论复试/期末课后习题复习均适用
-包括
-【重点复习笔记】
-2023版思想课重点笔记，期末重点一目了然
-【课后习题答案】
-每个章节的课后习题答案全收录，帮你巩固知识点，查漏补缺
-【题库及答案汇总】
-【知识点总结+思维导图】
-期末知识点和思维导图，大总结让你的复习更有针对性
+          <t>平面设计作品集模板毕设作业面试个人简历UI界面AI电商PSD素材PPT
+——★24小时自动秒发百度网盘 ★——
+——★24小时自动秒发百度网盘 ★——
+——★24小时自动秒发百度网盘 ★——
+600款设计师作品集 品牌电商 海报插画 U界面 面试求职
+宝贝秒拍秒发，拍下全发！你想要各种素材都在这里 任何不满意直接退款！！！
+如果没有及时回复可以先拍下来看是否需要和满意，不满意没有需要直接退款即可，上线会立即处理，您放心。
+预览图对应相应源文件名字，不是卖图片，也没有任何额外费用，如果不会使用可以咨询解决
+每套风格的模版都是我精心挑选出来的。
+每款精选质量高，适用于任何场合～
+每个风格都有单独归类文档编号
 </t>
         </is>
       </c>
       <c r="C16" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01Iz9Xxm1XV4lmU929S_!!4611686018427380176-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01Iz9Xxm1XV4lmU929S_!!4611686018427380176-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/O1CN01Iz9Xxm1XV4lmU929S_!!4611686018427380176-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01MyDvtg1dZ5x4MNzra_!!4611686018427387605-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01MyDvtg1dZ5x4MNzra_!!4611686018427387605-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i4/O1CN01MyDvtg1dZ5x4MNzra_!!4611686018427387605-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D16" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.17.1b377e61Ma7Ms3&amp;id=975519024031&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.17.1b377e61Ma7Ms3&amp;id=975519024031&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.17.1b377e61Ma7Ms3&amp;id=975519024031&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.22e26c82v4o1nV&amp;id=991558660076&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.22e26c82v4o1nV&amp;id=991558660076&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.22e26c82v4o1nV&amp;id=991558660076&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="17" ht="25.5" customHeight="1">
       <c r="A17">
-        <v>807129218718</v>
+        <v>763948096914</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>
-沪科版初中数学，七到九年级讲义
-讲义按照课本章节整理，每章分为基础版和提高版，两版都有知识点讲解和配套巩固练习。
-适合在校老师课堂知识专题讲解、课外辅导一对一或班课直接使用。
-其中一册为1元，全套5元（送一个中考总复习）。
-需要直接拍，系统会自动发货。
-新教材新题，版权所有，有完整创作时间线，禁止翻卖，资料翻卖会追究。认准正版，根据新教材更新资料。
-</t>
+          <t>述职PPT模板精选推荐95套述职报告ppt模板工作汇报年终总结PPT年中计划简约商务通用部门岗位述职
+精选述职报告PPT，岗位述职，年终总结，年中汇报等都有
+年终总结PPT模板 述职答辩PPT模板
+红色商务PPT模板
+每套模板都是精挑细选的，放心拍放心拍
+WPS和office编辑，简单编辑就能用
+在线发货，拍下即发。
+发货方式： b d 网盘发货
+因为产品具有可复制性，发货后不退换。
+产品价低，利润微薄，不满意可以联系客服，请不要随意差评，谢谢</t>
         </is>
       </c>
       <c r="C17" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN01PSr6AZ1WMXeruIeiu_!!0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN01PSr6AZ1WMXeruIeiu_!!0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i2/O1CN01PSr6AZ1WMXeruIeiu_!!0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN01gEDNJ127ygNBqDL6F_!!53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN01gEDNJ127ygNBqDL6F_!!53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i2/O1CN01gEDNJ127ygNBqDL6F_!!53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D17" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.4.1b377e61Ma7Ms3&amp;id=807129218718&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.4.1b377e61Ma7Ms3&amp;id=807129218718&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.4.1b377e61Ma7Ms3&amp;id=807129218718&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.18.22e26c82jlohwD&amp;id=763948096914&amp;categoryId=201453706", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.18.22e26c82jlohwD&amp;id=763948096914&amp;categoryId=201453706")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.18.22e26c82jlohwD&amp;id=763948096914&amp;categoryId=201453706</v>
       </c>
     </row>
     <row r="18" ht="25.5" customHeight="1">
       <c r="A18">
-        <v>887267029712</v>
+        <v>976139278954</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>黄夫人物理讲义新版旧版➕笔记电子版➕视频
-*拍下发货
-*发 度/夸
-一轮复习 一轮讲义 高一高二 高三复习 选修
-【免责声明】
-本店资源均通过网络等公开合法渠道获取，该资料仅作为阅读交流使用，并无任何商业目的，其版权归作者或出版社所有，本店不对所涉及的版权问题负法律责任。
-如版权方、出版社认为本店行为侵权、请立即通知本店删除物品。 商品所收取的费用，用于本店搜索整理，加工整改资料。
+          <t>结构化PPT模板：述职汇报PPT、工作汇报、实习汇报、论文答辩、财务分析、市场调研，模板内容可编辑
+适用范围：日常报告，市场调研，数据分析，工作总结，工作汇报，品牌效应……等各种场景
+黄金曲线模型，SWOT模型，冰山模型，鱼骨图……应有尽有
+300页高级逻辑数据PPT（赠500页汇报PPT）｜6种配色替换｜工作汇报、数据复盘、年中总结、个人介绍均适用｜可编辑数据｜打包价出！
+天蝎PPT，柠檬PPT，青云职场素材，唐峰素材，荔枝PPT，物语PPT，小李在做PPT，狗哥在做PPT，芝士PPT 全都有
+精美数据图
+精美逻辑图
+工作汇报
+可视化图表（可编辑）持续更新ing
+拍后赠送图标素材、工作汇报图标库、字体包
+原价拍下只发一个博主随时可拍，发送百度网盘链接，发后不退！建议看清楚再下单。
 </t>
         </is>
       </c>
       <c r="C18" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01WhNlX61MCKjVEzdC0_!!4611686018427382374-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01WhNlX61MCKjVEzdC0_!!4611686018427382374-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/O1CN01WhNlX61MCKjVEzdC0_!!4611686018427382374-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN01R36nyf1SnKTcyh1TG_!!4611686018427381555-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN01R36nyf1SnKTcyh1TG_!!4611686018427381555-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i2/O1CN01R36nyf1SnKTcyh1TG_!!4611686018427381555-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D18" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.15.1b377e61Ma7Ms3&amp;id=948092826007&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.15.1b377e61Ma7Ms3&amp;id=948092826007&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.15.1b377e61Ma7Ms3&amp;id=948092826007&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.18.22e26c82jlohwD&amp;id=976139278954&amp;categoryId=201453706", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.18.22e26c82jlohwD&amp;id=976139278954&amp;categoryId=201453706")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.18.22e26c82jlohwD&amp;id=976139278954&amp;categoryId=201453706</v>
       </c>
     </row>
     <row r="19" ht="25.5" customHeight="1">
       <c r="A19">
-        <v>948092826007</v>
+        <v>974574219628</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2023版马克思主义基本原理PDF电子版，
-高等教育出版社正版教材，
-本科考研政治必备。
-baidu网盘直接发链接，速度超快，其他相关资料也可以咨询我。
-［秒发］
+          <t>560页高端PPT模板，领导喜欢的7色逻辑架构图，数据分析可视化模板
+专业职场通用，年终总结汇报必备
+内容丰富，有逻辑有颜值，适合各类工作汇报
+自动发货，拍下秒发，24小时发货
+包含完整PPT源文件，可以直接使用
+文件格式：PPTX
+发货方式：网盘发送
+拍下自动发货，无需等待
+电子虚拟商品，售出不退不换
 </t>
         </is>
       </c>
       <c r="C19" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01J5ejnk2KKv8sKdusi_!!4611686018427387555-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01J5ejnk2KKv8sKdusi_!!4611686018427387555-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/O1CN01J5ejnk2KKv8sKdusi_!!4611686018427387555-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN0179nwvl1VQNTXESH79_!!4611686018427382007-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN0179nwvl1VQNTXESH79_!!4611686018427382007-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i2/O1CN0179nwvl1VQNTXESH79_!!4611686018427382007-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D19" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.7.1b377e61Ma7Ms3&amp;id=999178498819&amp;categoryId=201460510", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.7.1b377e61Ma7Ms3&amp;id=999178498819&amp;categoryId=201460510")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.7.1b377e61Ma7Ms3&amp;id=999178498819&amp;categoryId=201460510</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.5.22e26c82jlohwD&amp;id=974574219628&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.5.22e26c82jlohwD&amp;id=974574219628&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.5.22e26c82jlohwD&amp;id=974574219628&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="20" ht="25.5" customHeight="1">
       <c r="A20">
-        <v>973706589536</v>
+        <v>999620272606</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>【非常全面】自考15040《新思想概论》
-资料很全含2504精讲视频、2504串讲、历年真题（更新到最新）、讲义、复习资料！
-发货：拍下速发度盘。
-退换：电子版资料，一经售出，不退不换，敬请谅解！
-赠送：复习资料
-拍下默认自动发本科目全部资料
-全部为高清版，可网盘在线观看！
-格式排版清晰，可直接打印！
-有遗漏或者链接失效请私信我，看到后立即解决！！！
-祝所有考生顺利通关，拿本科证！
-</t>
+          <t>【红色商务】PPT模板述职汇报年中年终总结工作计划商务通用高端
+内容亮点：
+- 229套红色商务PPT模板，适合年终总结、述职汇报、工作计划等场景
+- 内容涵盖年度工作总结、项目展示、工作进度计划等模块
+- 红色商务风格，图文并茂，专业规范，适合企业、单位、个人使用
+获取方式：
+- 直接拍下，自动秒发网盘链接，手机平板电脑都能用
+- 资料为电子版，不是实物，不退不换
+版权声明：
+- 资料来源网络，仅供学习交流，版权归原作者所有
+- 电子资料售出不退不换，感谢理解
+有问题随时私聊，喜欢直接拍！</t>
         </is>
       </c>
       <c r="C20" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01BQCkTH1dcl6himpqe_!!4611686018427382637-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01BQCkTH1dcl6himpqe_!!4611686018427382637-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/O1CN01BQCkTH1dcl6himpqe_!!4611686018427382637-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01A9IGqw1IFlJB4zfSK_!!4611686018427383856-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01A9IGqw1IFlJB4zfSK_!!4611686018427383856-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i4/O1CN01A9IGqw1IFlJB4zfSK_!!4611686018427383856-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D20" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.1b377e61Ma7Ms3&amp;id=973706589536&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.1b377e61Ma7Ms3&amp;id=973706589536&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.1b377e61Ma7Ms3&amp;id=973706589536&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.22e26c82v4o1nV&amp;id=999620272606&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.22e26c82v4o1nV&amp;id=999620272606&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.22e26c82v4o1nV&amp;id=999620272606&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="21" ht="25.5" customHeight="1">
       <c r="A21">
-        <v>945296404459</v>
+        <v>1013558906432</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>【秒发】2025高一高二高三全国各地名校试卷真题库 语文数学英语物理化学生物政治地理历史试卷电子版
-[红圆]详情
-[1]高一：2024.7-2025.7，目前已整理至25年5月，包更新至25年7月。
-[2]高二：2024.7-2025.7，目前已整理至25年5月，包更新至25年7月。
-[3]高三：2024.6-2025.6，目前已整理至25年5月，包更新至25年6月。
-[红圆]高考9科，按月整理，收录各地区名校试卷，掌握最新考试动态，助力高中学习冲刺。
-让你毫不费力就能搞定你想要的名校试卷，
-最重要的是我们为试卷配有详细的答案解析。
-[红圆]标价就是几个年级打包价。每个年级几千套试卷帮你掌握各地考试动态，适合教学工作者研究试题，也适合学生刷题！高中生必备试卷题库。试卷海量，不排除个别无答案，介意勿拍。
-❤️垫子资料，不发快递，如有需要自行打印，24小时自动发货，永久保存，随时打印，方便学习使用。
-❤️价格展示并非文件价值，而是资料整理费用，如有侵权，联系客服删除即可。
-⭕ 渡盘，自动秒发货！
-⭕️借搜TAG：
-教材，教辅，高考资料，高中复习资料，高考复习资料，期末考试资料，资料汇总，期末复习资料，资料总结，高中语文复习资料，高中数学复习资料，高中英语复习资料，高中物理化学生物复习资料，高中政治历史地理复习资料，重点，笔记，题库，知识点归纳，大题总结，资料合集，高考语文模拟卷，高考数学模拟卷，高考英语模拟卷，高考物理模拟卷，高考化学模拟卷，高考生物模拟卷，高考政治模拟卷，高考历史模拟卷，高考地理模拟卷，
-#学习资料教材</t>
+          <t>【秒发】2026年中小学寒假安全教育家长会主题班会PPT模板成品课件一封信
+佰渡盘自动发货
+资料齐全，内容丰富，适合中小学寒假安全教育家长会、主题班会、家长一封信等场景，直接套用省时省力！
+资料为电子版，非实物，拍下自动发网盘链接，24小时内秒发，不会用网盘的可以私聊我～
+本店所有商品均为虚拟商品，不发快递、不发物流、不发邮箱，因资料具有可复制性，售出不退不换！
+需要直接拍，有问题随时私聊，喜欢就拍吧～
+</t>
         </is>
       </c>
       <c r="C21" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01jwt8Fo2G0X2plNJAN_!!4611686018427381593-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01jwt8Fo2G0X2plNJAN_!!4611686018427381593-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/O1CN01jwt8Fo2G0X2plNJAN_!!4611686018427381593-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i1/2200545133819/O1CN011p1EYz1e59h3i7fBh_!!4611686018427380987-53-xy_item.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i1/2200545133819/O1CN011p1EYz1e59h3i7fBh_!!4611686018427380987-53-xy_item.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i1/2200545133819/O1CN011p1EYz1e59h3i7fBh_!!4611686018427380987-53-xy_item.heic_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D21" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.14.1b377e61Ma7Ms3&amp;id=945296404459&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.14.1b377e61Ma7Ms3&amp;id=945296404459&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.14.1b377e61Ma7Ms3&amp;id=945296404459&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.21.22e26c82v4o1nV&amp;id=1013558906432&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.21.22e26c82v4o1nV&amp;id=1013558906432&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.21.22e26c82v4o1nV&amp;id=1013558906432&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="22" ht="25.5" customHeight="1">
       <c r="A22">
-        <v>941464310692</v>
+        <v>1009486555572</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>小学英语语法小升初语法知识点练习题，复习整理，小升初衔接巩固【自动免拼发货】
-58页电子版练习资料，PDF直接打印，含语法知识点和专项练习，讲解很全面，通熟易懂，巩固语法的不二之选！
-全国教材通用，不管是人教版，外研版，牛津版等都适用的！
-有需要直接拍下，百。度。网。盘。分。享！
-虚拟商品 不接受退换哦！
-发的是百 度 网 盘 链 接，永不失效，售出不退。
------★24小时自动发货，直接拍秒发★-----因素材具有可复制性，一经发货，概不退款！
+          <t>2026马年快闪ppt模板新年年会led背景视频颁奖典礼晚会开场倒计时
+下面图片介绍资源全部打包发你非常超值
+【全部打包网盘自动发货】需要的直接点我想要，购买就可以，然后我发你课程网盘链接，你打开链接保存到自己网盘，永久观看哦
 </t>
         </is>
       </c>
       <c r="C22" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN014SSFGI2JBvkNJlebQ_!!4611686018427386760-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN014SSFGI2JBvkNJlebQ_!!4611686018427386760-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i2/O1CN014SSFGI2JBvkNJlebQ_!!4611686018427386760-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i1/O1CN01Zg79dd2DGc9XYIGjR_!!4611686018427387046-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i1/O1CN01Zg79dd2DGc9XYIGjR_!!4611686018427387046-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i1/O1CN01Zg79dd2DGc9XYIGjR_!!4611686018427387046-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D22" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.1b377e61Ma7Ms3&amp;id=941464310692&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.1b377e61Ma7Ms3&amp;id=941464310692&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.1b377e61Ma7Ms3&amp;id=941464310692&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.28.22e26c82v4o1nV&amp;id=1009486555572&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.28.22e26c82v4o1nV&amp;id=1009486555572&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.28.22e26c82v4o1nV&amp;id=1009486555572&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="23" ht="25.5" customHeight="1">
       <c r="A23">
-        <v>991304162422</v>
+        <v>894666835900</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>计算机408考研资料合集，包含408八套卷答案解析、26竟成模拟题及解析、26零壹模拟卷，灰灰考研八套26年模拟题等。
-百度网盘发货，包含完整电子版资料，按年份分类整理。
-拍下稍等一会即可获得链接，后续会一直更新。
+          <t>900套企业宣传ppt模板公司介绍ppt产品介绍ppt
+涵盖各行各业，适用于公司简介、产品简介等场景；
+一份好的ppt可以助力您的事业，节省您的时间；
+可编辑可修改，使用方便；
+——————★24小时自动发货★——————
+精心挑选ppt高端模板，简洁、高效、直观；
+✨每套模板都是我精心挑选的；
+✨每款精品质量高，助力您更加顺利～
+✨小说明：网页端、手机端可能存在兼容问题，如碰到PPT显示异常，请下载后使用电脑端office和wps打开～
+虚拟物品售出不退不换噢！
+感兴趣的话快点击“我想要”来私聊吧！
 </t>
         </is>
       </c>
       <c r="C23" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01lYbcAp1n4XgnbSNrB_!!4611686018427380556-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01lYbcAp1n4XgnbSNrB_!!4611686018427380556-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/O1CN01lYbcAp1n4XgnbSNrB_!!4611686018427380556-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i3/O1CN01hAF0YS1Tsee9GkAo1_!!4611686018427386534-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i3/O1CN01hAF0YS1Tsee9GkAo1_!!4611686018427386534-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i3/O1CN01hAF0YS1Tsee9GkAo1_!!4611686018427386534-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D23" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.1b377e61Ma7Ms3&amp;id=991304162422&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.1b377e61Ma7Ms3&amp;id=991304162422&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.1b377e61Ma7Ms3&amp;id=991304162422&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.24.22e26c82v4o1nV&amp;id=894666835900&amp;categoryId=201453706", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.24.22e26c82v4o1nV&amp;id=894666835900&amp;categoryId=201453706")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.24.22e26c82v4o1nV&amp;id=894666835900&amp;categoryId=201453706</v>
       </c>
     </row>
     <row r="24" ht="25.5" customHeight="1">
       <c r="A24">
-        <v>974278541118</v>
+        <v>867027686359</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>出高中匠心地理课件 高中全部包含[上]
-❗️人教版[hot]
-包含：
-匠心必修一课件
-匠心必修二课件
-匠心选择性必修一课件
-匠心选择性必修二课件
-匠心选择性必修三课件
-匠心区域地理课件（中国和世界地理）
-匠心高三复习课件一轮二轮
-赠送：匠心微专题课件
-标价就是打包价
-特殊商品
-不退不换
-感兴趣的话点“我想要”，直接下单～
-</t>
+          <t>四色1000页数据贝恩商赛PPT模板，适用工作总结、财务分析、市场调研，内容可编辑。24小时内秒发！
+【好模板，值得拥有】
+- 四色任选：蓝色、红色、橙色、绿色
+- 高端双色设计，模拟麦肯锡等咨询公司风格
+- 适用范围广：日常报告、市场调研、数据分析等
+【注意】：网页端、手机端可能有兼容性问题，如显示异常请下载电脑端office和wps查看。
+需要的朋友直接拍下，我会第一时间发货。
+###发布技能来赚钱</t>
         </is>
       </c>
       <c r="C24" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN01sDL8ym2K1E84FFNj7_!!4611686018427386056-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN01sDL8ym2K1E84FFNj7_!!4611686018427386056-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i2/O1CN01sDL8ym2K1E84FFNj7_!!4611686018427386056-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01rCLaWD1oMgvEUqrJX_!!4611686018427387179-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01rCLaWD1oMgvEUqrJX_!!4611686018427387179-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i4/O1CN01rCLaWD1oMgvEUqrJX_!!4611686018427387179-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D24" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.14.1b377e61Ma7Ms3&amp;id=974278541118&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.14.1b377e61Ma7Ms3&amp;id=974278541118&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.14.1b377e61Ma7Ms3&amp;id=974278541118&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.28.22e26c82v4o1nV&amp;id=867027686359&amp;categoryId=201453706", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.28.22e26c82v4o1nV&amp;id=867027686359&amp;categoryId=201453706")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.28.22e26c82v4o1nV&amp;id=867027686359&amp;categoryId=201453706</v>
       </c>
     </row>
     <row r="25" ht="25.5" customHeight="1">
       <c r="A25">
-        <v>953373572384</v>
+        <v>1003448282930</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>宏观经济学第十版第十一版曼昆pdf笔记、教材➕练习题➕课后习题答案期末考试重点复习
-标价即拍价
-价格绝对市面最低
-#学习资料教材 #笔记学习资料
-</t>
+          <t>147套人工智能PPT模板｜蓝色科技风｜机器人主题｜动态效果｜大数据展示
+人工智能PPT机器人AI高科技感互联网大数据大气动态商务PPT模板
+内容涵盖机器人主题、科技感动态、大数据分析、人工智能介绍、科技工作汇报、产品发布、商务会议演示、未来科技展示、动态图表、科技报告等，适合互联网、大数据、商务汇报、产品发布、会议演示等多种场景，视觉冲击力强，提升演示效果。
+电子资料，拍下自动发网盘链接，24小时内秒发，虚拟商品不退不换。
+资料来源网络公开渠道，仅供学习交流，如有侵权请联系删除。</t>
         </is>
       </c>
       <c r="C25" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN01cZnkyT1ZuqGfzWFgv_!!4611686018427383943-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN01cZnkyT1ZuqGfzWFgv_!!4611686018427383943-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i2/O1CN01cZnkyT1ZuqGfzWFgv_!!4611686018427383943-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i1/O1CN01XVvPkb1IFlJQlRyKF_!!4611686018427383856-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i1/O1CN01XVvPkb1IFlJQlRyKF_!!4611686018427383856-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i1/O1CN01XVvPkb1IFlJQlRyKF_!!4611686018427383856-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D25" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.1b377e61Ma7Ms3&amp;id=953373572384&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.1b377e61Ma7Ms3&amp;id=953373572384&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.23.1b377e61Ma7Ms3&amp;id=953373572384&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.29.22e26c82v4o1nV&amp;id=1003448282930&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.29.22e26c82v4o1nV&amp;id=1003448282930&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.29.22e26c82v4o1nV&amp;id=1003448282930&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="26" ht="25.5" customHeight="1">
       <c r="A26">
-        <v>947259655001</v>
+        <v>995010492238</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026新高考数学题型全解Word版学生版和教师版
-讲义覆盖高考所有题型， 选用的例题和练习题大多来自历年新高考真题以及各省市的优质模拟题，让学生在练习过程中熟悉高考的命题风格和难度，提前适应高考节奏
-同时，对真题进行详细的分类和解析，帮助学生把握高考的重点和热点，明确复习方向。知识系统梳理：在讲解题型的同时，对相关的数学知识进行系统梳理，帮助学生构建完整的知识体系。
-讲义分学生版+教师版
-提供原版Word，可编辑，可打印。
-适用于高考数学一轮复习，高中数学必备！
+          <t>小学家长会ppt成品模板演讲稿暖场视频一二三四五六年级上下学期
+——★24小时自动秒发百度网盘 ★——
+——★24小时自动秒发百度网盘 ★——
+——★24小时自动秒发百度网盘 ★——
+2025年小学生家长会1-6年级上/下分类
+可编辑 精选实用
+成品PPT+发言稿+暖场视频
+宝贝秒拍秒发，拍下全发！你想要各种素材都在这里 任何不满意直接退款！！！
+如果没有及时回复可以先拍下来看是否需要和满意，不满意没有需要直接退款即可，上线会立即处理，您放心。
+预览图对应相应源文件名字，不是卖图片，也没有任何额外费用，如果不会使用可以咨询解决
+每套风格的模版都是我精心挑选出来的。
+每款精选质量高，适用于任何场合～
+每个风格都有单独归类文档编号
 </t>
         </is>
       </c>
       <c r="C26" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01l4QwAz1wFNZU4tTBb_!!4611686018427382502-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01l4QwAz1wFNZU4tTBb_!!4611686018427382502-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/O1CN01l4QwAz1wFNZU4tTBb_!!4611686018427382502-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN018ejMLH1dZ5xGmH2OR_!!4611686018427387605-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN018ejMLH1dZ5xGmH2OR_!!4611686018427387605-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i4/O1CN018ejMLH1dZ5xGmH2OR_!!4611686018427387605-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D26" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.4.1b377e61Ma7Ms3&amp;id=947259655001&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.4.1b377e61Ma7Ms3&amp;id=947259655001&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.4.1b377e61Ma7Ms3&amp;id=947259655001&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.12.22e26c82jlohwD&amp;id=995010492238&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.12.22e26c82jlohwD&amp;id=995010492238&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.12.22e26c82jlohwD&amp;id=995010492238&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="27" ht="25.5" customHeight="1">
       <c r="A27">
-        <v>1002329045198</v>
+        <v>1001203797915</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>最新版思想课期末冲刺包！复习笔记+考题+答案+知识点总结，大一到大三全覆盖！
-考研政治笔试/考研马理论复试/期末课后习题复习都能用！
-标价直接拍，拍下秒发网盘链接，自动发货，15秒到手！
-【重点复习笔记】
-2023版思想课重点笔记，期末冲刺一目了然！
-【课后习题答案】
-每个章节课后习题答案全收录，查漏补缺，巩固知识点！
-【题库+答案汇总】
-题库+答案汇总，刷题必备！
-【知识点总结+思维导图】
-期末知识点+思维导图，总结复习更高效！
-资料为电子版，网盘自动发货，拍下即发，虚拟商品，售出不退不换！
-需要直接拍，喜欢私聊，细节可问！
-</t>
+          <t>2025全新整理拼音PPT课件动画视频练习 幼小衔接电子版全|||
+套资料
+2025全套趣味拼音学习｜可打印
+有一种“苦”叫带娃学拼音，拼音是汉字发音的基础，往往是一大难点；
+这次精心整理了一套非常全面的资源，包含拼音的全部知识点；
+内有视频、动漫、游戏、练习、PPT等，从O开始，帮助小朋友轻松掌握基础内容；
+适合幼儿园、小学阶段使用；
+只要用心坚持，孩子一定会兴趣盎然，事半功倍！
+温馨提示：电子版资料，售出不退，如有问题，请在客服聊天窗口留言，看到后第一时间回复，谢谢！
+#早教神器来啦﻿ ﻿#9#拼音天练习﻿ ﻿#幼小衔接拼音拼音启蒙﻿ ﻿#幼儿园﻿ ﻿#在家早教﻿ ﻿#儿童拼音学习﻿</t>
         </is>
       </c>
       <c r="C27" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i4/O1CN01jwXvXb2Kw1GICKvHj_!!4611686018427386580-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i4/O1CN01jwXvXb2Kw1GICKvHj_!!4611686018427386580-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i4/O1CN01jwXvXb2Kw1GICKvHj_!!4611686018427386580-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i1/O1CN01Fj9Fdg1IFlJJFM048_!!4611686018427383856-53-fleamarket.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i1/O1CN01Fj9Fdg1IFlJJFM048_!!4611686018427383856-53-fleamarket.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i1/O1CN01Fj9Fdg1IFlJJFM048_!!4611686018427383856-53-fleamarket.heic_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D27" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.1b377e61Ma7Ms3&amp;id=1002329045198&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.1b377e61Ma7Ms3&amp;id=1002329045198&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.3.1b377e61Ma7Ms3&amp;id=1002329045198&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.15.22e26c82v4o1nV&amp;id=1001203797915&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.15.22e26c82v4o1nV&amp;id=1001203797915&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.15.22e26c82v4o1nV&amp;id=1001203797915&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="28" ht="25.5" customHeight="1">
       <c r="A28">
-        <v>953038530018</v>
+        <v>975639596553</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>【B170秒发货】[火]2025新人教版版高中高考政治必背知识点清单梳理选必修一二三四选修123电子资料高考总复习一轮复习二轮复习
-高中全年级必修+选修7册知识点梳理（填空版+背诵版）
-[钉子]word格式，每单元两份，一份挖空版一份背诵版有答案
-[红圆]课本是新人教版才可以用，如图所示，课本不一样勿拍！！！
-[右]点击“直接刀成”5秒内发货
-发摆渡
-页数如图四所示</t>
+          <t>170页高级感红色系PPT模板，图文排版超棒！
+全新更新到170页，买即得最新版本！
+一图到多图，各种形式都有，轻松做出高级感！
+所有元素可编辑，图片可换，一键换色超方便！
+直接套用，效果赞！标价即卖价哦～
+拍下自动发货，白度网盘链接发货，不退不换哈～
+学习资料教材 办公家具
+</t>
         </is>
       </c>
       <c r="C28" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i3/O1CN01gt0E3U2L9l6nysNUy_!!4611686018427380306-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i3/O1CN01gt0E3U2L9l6nysNUy_!!4611686018427380306-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i3/O1CN01gt0E3U2L9l6nysNUy_!!4611686018427380306-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i1/O1CN012ggqM21svHMQ6z9f6_!!4611686018427381684-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i1/O1CN012ggqM21svHMQ6z9f6_!!4611686018427381684-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i1/O1CN012ggqM21svHMQ6z9f6_!!4611686018427381684-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D28" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.13.1b377e61Ma7Ms3&amp;id=953038530018&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.13.1b377e61Ma7Ms3&amp;id=953038530018&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.13.1b377e61Ma7Ms3&amp;id=953038530018&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.11.22e26c82jlohwD&amp;id=975639596553&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.11.22e26c82jlohwD&amp;id=975639596553&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.11.22e26c82jlohwD&amp;id=975639596553&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="29" ht="25.5" customHeight="1">
       <c r="A29">
-        <v>989632758919</v>
+        <v>1015555988422</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>26➕25武忠祥选填技巧课，选填技巧课26
-26【视频课】讲解持续实时更新中，25视频课完整版
-26更新没那么快，复习进度快着急学习的孩子们，可以考虑看25版哦！
-视频mp4格式（没有sz格式），不需要播放器播放
-网盘（百度网盘、夸克网盘）自动发货
-链接清单
-一、26选填技巧【视频课】+【视频板书】（实时更新中）
-二、25选填技巧【视频课】+【视频板书】（完整版）
-三、25武忠祥《解题密码 选填题》练习题详解
-武忠祥选填技巧课质量极高，考生不能错过哦~~
-祝广大学子学业有成！
+          <t>4款年会游戏PPT模板 元旦新年公司游戏互动包你画我猜谁是卧底职场团建
+职场人办年会团建不用愁！一套搞定现场互动游戏PPT模板，直接拿来就能用。
+互动游戏PPT：谐音梗挑战 + 你画我猜 + 看emoji猜成语 + 谁是卧底。
+每款游戏均已配好详细规则、素材和题目，无需自己费心找题写流程，打开即可直接使用。
+活泼黄黑漫画风，气氛十足，适用于企业年会、部门团建、尾牙宴等多种场合。
+内容可编辑可修改，拿到后可根据需要进行调整，轻松应对各种现场需求。
+【获取方式】
+拍下后秒发百度网盘链接，自动发货，即时到手。
+省时省力，帮你高效搞定年会游戏环节，活跃气氛不冷场！
+免责声明： 本商品为虚拟资料，版权归属原作者。如认为侵犯版权，请及时通知小店删除。支持正版，敬请前往官方购买。
 </t>
         </is>
       </c>
       <c r="C29" s="2" t="str">
-        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i2/O1CN01bO1Uby23XQWFiOyU0_!!4611686018427379761-0-fleamarket.jpg_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i2/O1CN01bO1Uby23XQWFiOyU0_!!4611686018427379761-0-fleamarket.jpg_790x10000Q90.jpg_.webp")</f>
-        <v>img.alicdn.com/bao/uploaded/i2/O1CN01bO1Uby23XQWFiOyU0_!!4611686018427379761-0-fleamarket.jpg_790x10000Q90.jpg_.webp</v>
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i1/2221187899404/O1CN01MYtPzM2JL5imjGReM_!!4611686018427379724-53-xy_item.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i1/2221187899404/O1CN01MYtPzM2JL5imjGReM_!!4611686018427379724-53-xy_item.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i1/2221187899404/O1CN01MYtPzM2JL5imjGReM_!!4611686018427379724-53-xy_item.heic_790x10000Q90.jpg_.webp</v>
       </c>
       <c r="D29" s="2" t="str">
-        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.20.1b377e61Ma7Ms3&amp;id=989632758919&amp;categoryId=202036301", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.20.1b377e61Ma7Ms3&amp;id=989632758919&amp;categoryId=202036301")</f>
-        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.20.1b377e61Ma7Ms3&amp;id=989632758919&amp;categoryId=202036301</v>
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.27.22e26c82v4o1nV&amp;id=1015555988422&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.27.22e26c82v4o1nV&amp;id=1015555988422&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.27.22e26c82v4o1nV&amp;id=1015555988422&amp;categoryId=201454708</v>
       </c>
     </row>
     <row r="30" ht="25.5" customHeight="1">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" ht="25.5" customHeight="1">
-      <c r="A31"/>
-      <c r="B31"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="A30">
+        <v>1005840222093</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>【0.1双盘秒发】2026马年元旦游戏联欢晚会PPT
+2026马年元旦游戏联欢晚会PPT课件，81页 可修改编辑
+内容丰富，适合班级、学校、幼儿园元旦活动，互动性强，包含多种小游戏和活动环节，目录清晰，直接拿来用很方便
+PPT文件，可编辑修改
+拍下发网盘链接
+标价即售价 直接拍就行 能拍就是有货
+不用问在不在 拼单看到就会点免拼
+</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="str">
+        <f>=HYPERLINK("http://img.alicdn.com/bao/uploaded/i3/2221166003364/O1CN01vCpg6A1ailTioItVW_!!4611686018427380900-53-xy_item.heic_790x10000Q90.jpg_.webp", "img.alicdn.com/bao/uploaded/i3/2221166003364/O1CN01vCpg6A1ailTioItVW_!!4611686018427380900-53-xy_item.heic_790x10000Q90.jpg_.webp")</f>
+        <v>img.alicdn.com/bao/uploaded/i3/2221166003364/O1CN01vCpg6A1ailTioItVW_!!4611686018427380900-53-xy_item.heic_790x10000Q90.jpg_.webp</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f>=HYPERLINK("https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.21.22e26c82v4o1nV&amp;id=1005840222093&amp;categoryId=201454708", "https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.21.22e26c82v4o1nV&amp;id=1005840222093&amp;categoryId=201454708")</f>
+        <v>https://www.goofish.com/item?spm=a21ybx.search.searchFeedList.21.22e26c82v4o1nV&amp;id=1005840222093&amp;categoryId=201454708</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
